--- a/Config/PvpModeConfig.xlsx
+++ b/Config/PvpModeConfig.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,12 +467,17 @@
           <t>RankReward</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RankScore</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>DamageRoundScale</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>OpenPhaseSeconds</t>
         </is>
@@ -514,12 +519,17 @@
           <t>int[]</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int[]</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -561,12 +571,17 @@
           <t>第1到4名奖励</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>第1到4名局外PVP分数加减</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>每轮伤害加成</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>选牌秒数</t>
         </is>
@@ -608,12 +623,17 @@
           <t>200|120|60|30</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>50|25|0|-40</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" s="1" t="n">
         <v>20</v>
       </c>
     </row>

--- a/Config/PvpModeConfig.xlsx
+++ b/Config/PvpModeConfig.xlsx
@@ -467,7 +467,7 @@
           <t>RankReward</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>RankScore</t>
         </is>
@@ -519,7 +519,7 @@
           <t>int[]</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>int[]</t>
         </is>
@@ -571,7 +571,7 @@
           <t>第1到4名奖励</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>第1到4名局外PVP分数加减</t>
         </is>
@@ -603,10 +603,8 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
+      <c r="D4" s="1" t="n">
+        <v>250</v>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
@@ -623,7 +621,7 @@
           <t>200|120|60|30</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>50|25|0|-40</t>
         </is>

--- a/Config/PvpModeConfig.xlsx
+++ b/Config/PvpModeConfig.xlsx
@@ -626,10 +626,8 @@
           <t>50|25|0|-40</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
+      <c r="I4" s="1" t="n">
+        <v>0.05</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>20</v>
